--- a/Hisui_Paths.xlsx
+++ b/Hisui_Paths.xlsx
@@ -11901,7 +11901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Defeat Gym - Kleavor</t>
+          <t>Defeat 10 Pokemon in Jubilife Village</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unlock Crimson Mirelands (Golden Lowlands North)</t>
+          <t>Unlock Jubilife Village Daycare</t>
         </is>
       </c>
     </row>
@@ -11946,12 +11946,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Defeat Gym - Lilligant</t>
+          <t>Visit Jubilife Village Daycare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unlock Cobalt Coastlands (Crossing Slope)</t>
+          <t>Unlock Aspiration Hill</t>
         </is>
       </c>
     </row>
@@ -11963,12 +11963,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Defeat Gym - Arcanine</t>
+          <t>Defeat 10 Pokemon in Aspiration Hill</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unlock Coronet Highlands (Celestica Trail)</t>
+          <t>Unlock Horseshoe Plains</t>
         </is>
       </c>
     </row>
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Defeat Gym - Electrode</t>
+          <t>Defeat 10 Pokemon in Horseshoe Plains</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unlock Alabaster Icelands (Whiteout Valley)</t>
+          <t>Unlock Horseshoe Plains (Fishing Spot)</t>
         </is>
       </c>
     </row>
@@ -11997,12 +11997,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Defeat Gym - Avalugg</t>
+          <t>Defeat 10 Pokemon in Horseshoe Plains (Fishing Spot) (Water)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unlock Clan Leaders Battles</t>
+          <t>Unlock Floaro Gardens</t>
         </is>
       </c>
     </row>
@@ -12014,12 +12014,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Defeat Gym - Warden Ingo</t>
+          <t>Defeat 10 Pokemon in Floaro Gardens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unlock Late Game Exploring (Worn Bridge)</t>
+          <t>Unlock Deertrack Path</t>
         </is>
       </c>
     </row>
@@ -12031,248 +12031,1761 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Complete Late Game Exploring</t>
+          <t>Defeat 10 Pokemon in Deertrack Path</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unlock Hisui Pokemon League</t>
+          <t>Unlock Deertrack Heights</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-1</t>
+          <t>Challenge 8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Defeat Gym - Kleavor</t>
+          <t>Defeat 10 Pokemon in Deertrack Heights</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unlock Space-Time Distortion (Level 1)</t>
+          <t>Unlock Gym - Kleavor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-2</t>
+          <t>Challenge 9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Defeat Gym - Lilligant</t>
+          <t>Defeat Gym - Kleavor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Unlock Space-Time Distortion (Level 2)</t>
+          <t>Unlock Oreburrow Tunnel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-3</t>
+          <t>Challenge 10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Defeat Gym - Avalugg</t>
+          <t>Defeat 10 Pokemon in Oreburrow Tunnel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Unlock Space-Time Distortion (Level 3)</t>
+          <t>Unlock Nature’s Pantry</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-4</t>
+          <t>Challenge 11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Defeat Hisui Pokemon League</t>
+          <t>Defeat 10 Pokemon in Nature’s Pantry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unlock Space-Time Distortion (Max Level)</t>
+          <t>Unlock The Heartwood North</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-1</t>
+          <t>Challenge 12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capture 10 Ghost Type Pokemon</t>
+          <t>Defeat 10 Pokemon in The Heartwood North</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unlock Wisp Encounter: Gastly / Haunter</t>
+          <t>Unlock The Heartwood South</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-2</t>
+          <t>Challenge 13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Defeat Gym - Arcanine &amp; Capture 30 Ghost Type Pokemon</t>
+          <t>Defeat 10 Pokemon in The Heartwood South</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unlock Wisp Encounter: Misdreavus / Mismagius</t>
+          <t>Unlock The Heartwood South (Fishing Spot)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-3</t>
+          <t>Challenge 14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Defeat Hisui Pokemon League &amp; Capture 50 Ghost Type Pokemon</t>
+          <t>Defeat 10 Pokemon in The Heartwood South (Fishing Spot) (Water)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unlock Spiritomb Encounter</t>
+          <t>Unlock Golden Lowlands North</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-1</t>
+          <t>Challenge 15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capture 10 different species in Crimson Mirelands</t>
+          <t>Defeat 10 Pokemon in Golden Lowlands North</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unlock Unown Ruins (A-F)</t>
+          <t>Unlock Golden Lowlands North (Fishing Spot)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-2</t>
+          <t>Challenge 16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capture 10 different species in Cobalt Coastlands</t>
+          <t>Defeat 10 Pokemon in Golden Lowlands North (Fishing Spot) (Water)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unlock Unown Ruins (G-L)</t>
+          <t>Unlock Golden Lowlands South</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-3</t>
+          <t>Challenge 17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capture 10 different species in Coronet Highlands</t>
+          <t>Defeat 10 Pokemon in Golden Lowlands South</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unlock Unown Ruins (M-S)</t>
+          <t>Unlock Golden Lowlands South (Fishing Spot)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-4</t>
+          <t>Challenge 18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capture 10 different species in Alabaster Icelands</t>
+          <t>Defeat 10 Pokemon in Golden Lowlands South (Fishing Spot) (Water)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unlock Unown Ruins (T-Z, !, ?)</t>
+          <t>Unlock Gapejaw Bog North</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Extra Challenge 4-1</t>
+          <t>Challenge 19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capture Uxie, Mesprit, Azelf</t>
+          <t>Defeat 10 Pokemon in Gapejaw Bog North</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unlock Red Chain Item</t>
+          <t>Unlock Gapejaw Bog North (Fishing Spot)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Extra Challenge 4-2</t>
+          <t>Challenge 20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Defeat Hisui Pokemon League &amp; Hold Red Chain</t>
+          <t>Defeat 10 Pokemon in Gapejaw Bog North (Fishing Spot) (Water)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unlock Dialga / Palkia Battle</t>
+          <t>Unlock Gapejaw Bog South</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Challenge 21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Gapejaw Bog South</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unlock Gapejaw Bog South (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Challenge 22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Gapejaw Bog South (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Lilligant</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Challenge 23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Lilligant</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Unlock Ursa's Ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Challenge 24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ursa's Ring</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Unlock Sludge Mound</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Challenge 25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Sludge Mound</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Unlock Scarlet Bog</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Challenge 26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Scarlet Bog</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Unlock Bolderoll Slope</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Challenge 27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Bolderoll Slope</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unlock Holm of Trials</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Challenge 28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Holm of Trials</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Unlock Holm of Trials (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Challenge 29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Holm of Trials (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Unlock Crossing Slope</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Challenge 30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Crossing Slope</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unlock Bathers' Lagoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Challenge 31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Bathers' Lagoon</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unlock Bathers' Lagoon (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Challenge 32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Bathers' Lagoon (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Unlock Castaway Shore</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Challenge 33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Castaway Shore</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Unlock Castaway Shore (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Challenge 34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Castaway Shore (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Arcanine</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Challenge 35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Arcanine</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Unlock Veilstone Cape</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Challenge 36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Veilstone Cape</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Unlock Tranquility Cove</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Challenge 37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Tranquility Cove</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Unlock Tranquility Cove (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Challenge 38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Tranquility Cove (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Unlock Islespy Shore</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Challenge 39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Islespy Shore</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Unlock Islespy Shore (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Challenge 40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Islespy Shore (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Unlock Seagrass Haven</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Challenge 41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Seagrass Haven</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Unlock Deadwood Haunt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Challenge 42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Deadwood Haunt</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Unlock Firespit Island</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Challenge 43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Firespit Island</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Unlock Spring Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Challenge 44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Spring Path</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Unlock Spring Path (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Challenge 45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Spring Path (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Unlock Celestica Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Challenge 46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Celestica Trail</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Unlock Celestica Ruins</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Challenge 47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Celestica Ruins</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Electrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Challenge 48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Electrode</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Unlock Clamberclaw Cliffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Challenge 49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Clamberclaw Cliffs</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Unlock Sacred Plaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Challenge 50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Sacred Plaza</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Unlock Stonetooth Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Challenge 51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Stonetooth Rows</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Unlock Primeval Grotto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Challenge 52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Primeval Grotto</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Unlock Primeval Grotto (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Challenge 53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Primeval Grotto (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Unlock Coronet Highlands</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Challenge 54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Coronet Highlands</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Unlock Fabled Spring</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Challenge 55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Fabled Spring</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Unlock Fabled Spring (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Challenge 56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Fabled Spring (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Unlock Whiteout Valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Challenge 57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Whiteout Valley</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Unlock Bonechill Wastes North</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Challenge 58</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Bonechill Wastes North</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Unlock Bonechill Wastes South</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Challenge 59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Bonechill Wastes South</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Avalugg</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Challenge 60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Avalugg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Unlock Icebound Falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Challenge 61</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Icebound Falls</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Unlock Arena's Approach</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Challenge 62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Arena's Approach</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Unlock Glacier Terrace</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Challenge 63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Glacier Terrace</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Unlock Snowpoint Temple</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Challenge 64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Snowpoint Temple</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Unlock Heart's Crag</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Challenge 65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Heart's Crag</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Unlock Heart's Crag (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Challenge 66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Heart's Crag (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Clan Leader Adaman</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Challenge 67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Clan Leader Adaman</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Clan Leader Irida</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Challenge 68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Clan Leader Irida</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Unlock Gym - Warden Ingo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Challenge 69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Warden Ingo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Unlock Worn Bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Challenge 70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Worn Bridge</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Unlock Worn Bridge (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Challenge 71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Worn Bridge (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Unlock Droning Meadow</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Challenge 72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Droning Meadow</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Unlock Grueling Grove</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Challenge 73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Grueling Grove</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Unlock Sandgem Flats North</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Challenge 74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Sandgem Flats North</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Unlock Sandgem Flats North (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Challenge 75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Sandgem Flats North (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Unlock Sandgem Flats South</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Challenge 76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Sandgem Flats South</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Unlock Sandgem Flats South (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Challenge 77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Sandgem Flats South (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Unlock Ginkgo Landing</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Challenge 78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ginkgo Landing</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Unlock Ginkgo Landing (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Challenge 79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ginkgo Landing (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Unlock Ramanas Island North</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Challenge 80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ramanas Island North</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Unlock Ramanas Island North (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Challenge 81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ramanas Island North (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Unlock Ramanas Island South</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Challenge 82</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ramanas Island South</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Unlock Ramanas Island South (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Challenge 83</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Ramanas Island South (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Unlock Obsidian Falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Challenge 84</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Obsidian Falls</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Unlock Obsidian Falls (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Challenge 85</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Obsidian Falls (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Unlock Lake Verity</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Challenge 86</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Lake Verity</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Unlock Lake Verity (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Challenge 87</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Lake Verity (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Unlock Lake Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Challenge 88</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Lake Valor</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Unlock Lake Valor (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Challenge 89</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Lake Valor (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Unlock Wayward Cave</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Challenge 90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Wayward Cave</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Unlock Wayward Cave (Fishing Spot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Challenge 91</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Wayward Cave (Fishing Spot) (Water)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Unlock Cloudpool Ridge North</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Challenge 92</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Cloudpool Ridge North</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Unlock Cloudpool Ridge South</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Challenge 93</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Cloudpool Ridge South</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Unlock Seaside Hollow</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Challenge 94</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Seaside Hollow</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Unlock Shrouded Ruins</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Challenge 95</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Shrouded Ruins</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Unlock Space-Time Distortion</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Challenge 96</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Space-Time Distortion</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Unlock Hisui Pokemon League</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Extra Challenge 1-1</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Kleavor</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Unlock Space-Time Distortion (Level 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Extra Challenge 1-2</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Lilligant</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Unlock Space-Time Distortion (Level 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Extra Challenge 1-3</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Avalugg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Unlock Space-Time Distortion (Level 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Extra Challenge 1-4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Defeat Hisui Pokemon League</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Unlock Space-Time Distortion (Max Level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Extra Challenge 2-1</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Capture 10 Ghost Type Pokemon</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Unlock Wisp Encounter: Gastly / Haunter</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Extra Challenge 2-2</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Defeat Gym - Arcanine &amp; Capture 30 Ghost Type Pokemon</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Unlock Wisp Encounter: Misdreavus / Mismagius</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Extra Challenge 2-3</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Defeat Hisui Pokemon League &amp; Capture 50 Ghost Type Pokemon</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Unlock Spiritomb Encounter</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Extra Challenge 3-1</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Capture 10 different species in Crimson Mirelands</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Unlock Unown Ruins (A-F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Extra Challenge 3-2</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Capture 10 different species in Cobalt Coastlands</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Unlock Unown Ruins (G-L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Extra Challenge 3-3</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Capture 10 different species in Coronet Highlands</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Unlock Unown Ruins (M-S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Extra Challenge 3-4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Capture 10 different species in Alabaster Icelands</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Unlock Unown Ruins (T-Z, !, ?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Extra Challenge 4-1</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Capture Uxie, Mesprit, Azelf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Unlock Red Chain Item</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Extra Challenge 4-2</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Defeat Hisui Pokemon League &amp; Hold Red Chain</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Unlock Dialga / Palkia Battle</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>Extra Challenge 4-3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Complete Hisui Pokedex (All Sheets)</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Unlock Arceus Battle (Temple of Sinnoh)</t>
         </is>

--- a/Hisui_Paths.xlsx
+++ b/Hisui_Paths.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E429"/>
+  <dimension ref="A1:E432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,7 +650,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rapidash</t>
+          <t>Wurmple</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -825,32 +825,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Horseshoe Plains</t>
+          <t>Deertrack Path</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wurmple</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>8-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Kricketot</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kricketot</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -900,32 +900,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deertrack Path</t>
+          <t>Deertrack Heights</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8-10</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Chimchar</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chimchar</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Munchlax</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Munchlax</t>
+          <t>Stantler</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1031,45 +1031,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deertrack Heights</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Stantler</t>
-        </is>
-      </c>
+          <t>Gym - Kleavor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10-12</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gym - Kleavor</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Oreburrow Tunnel</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Geodude</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>14-16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Luxio</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luxio</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Shinx</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shinx</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1192,32 +1192,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oreburrow Tunnel</t>
+          <t>Nature’s Pantry</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14-16</t>
+          <t>16-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Kricketot</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kricketot</t>
+          <t>Pichu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pichu</t>
+          <t>Kricketune</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kricketune</t>
+          <t>Paras</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Paras</t>
+          <t>Parasect</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Parasect</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Staraptor</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Staraptor</t>
+          <t>Staravia</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1417,32 +1417,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nature’s Pantry</t>
+          <t>The Heartwood North</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Staravia</t>
+          <t>Beautifly</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>16-17</t>
+          <t>17-19</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Beautifly</t>
+          <t>Dustox</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dustox</t>
+          <t>Wurmple</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wurmple</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Lopunny</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Heartwood North</t>
+          <t>The Heartwood South</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lopunny</t>
+          <t>Cascoon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17-19</t>
+          <t>19-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cascoon</t>
+          <t>Silcoon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Silcoon</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1698,26 +1698,26 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Heartwood South</t>
+          <t>Golden Lowlands North</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Kricketot</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19-21</t>
+          <t>21-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kricketot</t>
+          <t>Kricketune</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kricketune</t>
+          <t>Paras</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paras</t>
+          <t>Parasect</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Parasect</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Raichu</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1842,32 +1842,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Golden Lowlands North</t>
+          <t>Golden Lowlands South</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raichu</t>
+          <t>Pichu</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21-23</t>
+          <t>23-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pichu</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1992,32 +1992,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Golden Lowlands South</t>
+          <t>Gapejaw Bog North</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gapejaw Bog North</t>
+          <t>Gapejaw Bog South</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bibarel</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Yanma</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2367,76 +2367,76 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gapejaw Bog South</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Wormadam Sandy Cloak</t>
-        </is>
-      </c>
+          <t>Gym - Lilligant</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>27-29</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>11.1%</t>
-        </is>
-      </c>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Gapejaw Bog South</t>
+          <t>Ursa's Ring</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yanma</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>31-33</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gym - Lilligant</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Ursa's Ring</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Bidoof</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>31-33</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bibarel</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bidoof</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Yanma</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Teddiursa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yanma</t>
+          <t>Petilil</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2559,107 +2559,107 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ursa's Ring</t>
+          <t>Sludge Mound</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Teddiursa</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ursa's Ring</t>
+          <t>Scarlet Bog</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ursaring</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>34-36</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sludge Mound</t>
+          <t>Scarlet Bog</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>33-34</t>
+          <t>34-36</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sludge Mound</t>
+          <t>Scarlet Bog</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>33-34</t>
+          <t>34-36</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Skuntank</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Stunky</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2734,27 +2734,27 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scarlet Bog</t>
+          <t>Bolderoll Slope</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -2765,21 +2765,21 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scarlet Bog</t>
+          <t>Bolderoll Slope</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2790,21 +2790,21 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scarlet Bog</t>
+          <t>Bolderoll Slope</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Skuntank</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2815,26 +2815,26 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scarlet Bog</t>
+          <t>Bolderoll Slope</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Stunky</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Golem</t>
+          <t>Onix</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Rhyhorn</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Togetic</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2909,551 +2909,551 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Holm of Trials</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Holm of Trials</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Holm of Trials</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Onix</t>
+          <t>Electrode</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rhyhorn</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Togetic</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Holm of Trials</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Holm of Trials</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Holm of Trials</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Torterra</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Holm of Trials</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Toxicroak</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Bathers' Lagoon</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Togepi</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Bathers' Lagoon</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Bathers' Lagoon</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Castaway Shore</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>44-46</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Castaway Shore</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>44-46</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Castaway Shore</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Skorupi</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>44-46</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bathers' Lagoon</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Togepi</t>
-        </is>
-      </c>
+          <t>Gym - Arcanine</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>42-44</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bathers' Lagoon</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Beautifly</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>48-50</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bathers' Lagoon</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>48-50</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Castaway Shore</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Dustox</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>44-46</t>
+          <t>48-50</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Castaway Shore</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>44-46</t>
+          <t>48-50</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Castaway Shore</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>44-46</t>
+          <t>48-50</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Gym - Arcanine</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>Veilstone Cape</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Murkrow</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>48-50</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Beautifly</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dustox</t>
+          <t>Growlithe</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Vulpix</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3557,161 +3557,161 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
+          <t>Tranquility Cove</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
+          <t>Tranquility Cove</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
+          <t>Tranquility Cove</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Golem</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
+          <t>Islespy Shore</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>51-53</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
+          <t>Islespy Shore</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Growlithe</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>51-53</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
+          <t>Seagrass Haven</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Vulpix</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>53-55</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tranquility Cove</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3721,137 +3721,137 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>50-51</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tranquility Cove</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>50-51</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tranquility Cove</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Wyrdeer</t>
+          <t>Starly</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>50-51</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Islespy Shore</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>51-53</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Islespy Shore</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Petilil</t>
+          <t>Chatot</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>51-53</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Seagrass Haven</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ursaluna</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>53-55</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Dusknoir</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Duskull</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3907,351 +3907,351 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Starly</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Magby</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chatot</t>
+          <t>Magmar</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Ninetales</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dusknoir</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Magby</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Magmar</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Toxicroak</t>
+          <t>Chimecho</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Arcanine</t>
+          <t>Rhydon</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Steelix</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4301,182 +4301,182 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Bonsly</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chimecho</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Rhydon</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Steelix</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bonsly</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4507,343 +4507,343 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Bronzong</t>
-        </is>
-      </c>
+          <t>Gym - Electrode</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>63-65</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Gible</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Gabite</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Gym - Electrode</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>Sacred Plaza</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Burmy Plant Cloak</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>68-70</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Luxray</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Rotom</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Gabite</t>
+          <t>Chingling</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>68-70</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Rhyperior</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Voltorb</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4893,182 +4893,182 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Luxray</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Rotom</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chingling</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Rhyperior</t>
+          <t>Mismagius</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Voltorb</t>
+          <t>Rotom</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Torterra</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5099,21 +5099,21 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5124,21 +5124,21 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5149,21 +5149,21 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5174,21 +5174,21 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Scyther</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5199,21 +5199,21 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Mismagius</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5224,21 +5224,21 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Rotom</t>
+          <t>Gligar</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5249,21 +5249,21 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>Gliscor</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Probopass</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5299,121 +5299,121 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Goodra</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Garchomp</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Scyther</t>
+          <t>Avalugg</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Electivire</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Gligar</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -5424,21 +5424,21 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Gliscor</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5449,21 +5449,21 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Probopass</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5474,101 +5474,101 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Goodra</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Garchomp</t>
+          <t>Clefable</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avalugg</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Electivire</t>
+          <t>Cleffa</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5599,603 +5599,603 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Whiteout Valley</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Whiteout Valley</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Clefable</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Froslass</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Glalie</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Whiteout Valley</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Whiteout Valley</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Lopunny</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Swinub</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Froslass</t>
+          <t>Zoroark</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Glalie</t>
+          <t>Zorua</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Piloswine</t>
-        </is>
-      </c>
+          <t>Gym - Avalugg</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>80-82</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Crobat</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Lopunny</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Swinub</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Zoroark</t>
+          <t>Elekid</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Zorua</t>
+          <t>Lucario</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Gym - Avalugg</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr"/>
+          <t>Icebound Falls</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Riolu</t>
+        </is>
+      </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
+          <t>85-87</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Ambipom</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Duskull</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6205,22 +6205,22 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6230,62 +6230,62 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Lucario</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Riolu</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Ambipom</t>
+          <t>Bergmite</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Machamp</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6335,202 +6335,202 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Elekid</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bergmite</t>
+          <t>Abomasnow</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Machamp</t>
+          <t>Snover</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>89-91</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -6541,21 +6541,21 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -6566,21 +6566,21 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -6591,21 +6591,21 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -6616,21 +6616,21 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Braviary</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -6641,21 +6641,21 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Abomasnow</t>
+          <t>Gallade</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -6666,21 +6666,21 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Snover</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -6691,61 +6691,61 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Ambipom</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6755,22 +6755,22 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6780,320 +6780,320 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Braviary</t>
+          <t>Gardevoir</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Gallade</t>
+          <t>Rapidash</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Rufflet</t>
-        </is>
-      </c>
+          <t>Gym - Clan Leader Adaman</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>91-93</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Aipom</t>
-        </is>
-      </c>
+          <t>Gym - Clan Leader Irida</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>93-95</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Ambipom</t>
-        </is>
-      </c>
+          <t>Gym - Warden Ingo</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>93-95</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Kirlia</t>
-        </is>
-      </c>
+          <t>Hisui Pokemon League</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>93-95</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>101-102</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Worn Bridge</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Worn Bridge</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Gardevoir</t>
+          <t>Ursaring</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Droning Meadow</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Sneasler</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Gym - Clan Leader Adaman</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr"/>
+          <t>Droning Meadow</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Burmy Plant Cloak</t>
+        </is>
+      </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Gym - Clan Leader Irida</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr"/>
+          <t>Droning Meadow</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Wormadam Plant Cloak</t>
+        </is>
+      </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Gym - Warden Ingo</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
+          <t>Droning Meadow</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Grotle</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Hisui Pokemon League</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>Droning Meadow</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Pachirisu</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>101-102</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Worn Bridge</t>
+          <t>Droning Meadow</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Turtwig</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7103,22 +7103,22 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Worn Bridge</t>
+          <t>Droning Meadow</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Mamoswine</t>
+          <t>Vespiquen</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bibarel</t>
+          <t>Yanmega</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7159,16 +7159,16 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Beautifly</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7184,16 +7184,16 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7209,16 +7209,16 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Grotle</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7234,16 +7234,16 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Pachirisu</t>
+          <t>Dustox</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7259,16 +7259,16 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Turtwig</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7284,16 +7284,16 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Vespiquen</t>
+          <t>Heracross</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7309,16 +7309,16 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Yanmega</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Beautifly</t>
+          <t>Golem</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7353,22 +7353,22 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Luxio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7384,16 +7384,16 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Staravia</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7409,16 +7409,16 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Dustox</t>
+          <t>Abra</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7434,16 +7434,16 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7459,16 +7459,16 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Heracross</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -7484,16 +7484,16 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Luxray</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Luxio</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7528,22 +7528,22 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Staravia</t>
+          <t>Mime Jr.</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7559,16 +7559,16 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Abra</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7584,16 +7584,16 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Alakazam</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7609,16 +7609,16 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Kadabra</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7634,16 +7634,16 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Luxray</t>
+          <t>Mr. Mime</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Mime Jr.</t>
+          <t>Snorlax</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -7678,22 +7678,22 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Alakazam</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Kadabra</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -7753,22 +7753,22 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Mr. Mime</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7778,22 +7778,22 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Snorlax</t>
+          <t>Starly</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Drapion</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Arcanine</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7878,22 +7878,22 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Chimchar</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7903,22 +7903,22 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Starly</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Staravia</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7953,22 +7953,22 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Drapion</t>
+          <t>Infernape</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Chimchar</t>
+          <t>Monferno</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8009,16 +8009,16 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8028,22 +8028,22 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Staravia</t>
+          <t>Drifloon</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8053,22 +8053,22 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Infernape</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8078,22 +8078,22 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Monferno</t>
+          <t>Ursaluna</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8103,22 +8103,22 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Ramanas Island South</t>
+          <t>Obsidian Falls</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Blissey</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8128,22 +8128,22 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Ramanas Island South</t>
+          <t>Obsidian Falls</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Drifloon</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Ramanas Island South</t>
+          <t>Obsidian Falls</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Blissey</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Togepi</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8253,22 +8253,22 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Obsidian Falls</t>
+          <t>Lake Verity</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8278,22 +8278,22 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Obsidian Falls</t>
+          <t>Lake Valor</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Mamoswine</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8303,22 +8303,22 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Obsidian Falls</t>
+          <t>Wayward Cave</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Togepi</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8328,43 +8328,59 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Lake Verity</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr"/>
+          <t>Wayward Cave</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Crobat</t>
+        </is>
+      </c>
       <c r="D321" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Lake Valor</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>Wayward Cave</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Gible</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -8377,7 +8393,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Torterra</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8387,22 +8403,22 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Wayward Cave</t>
+          <t>Cloudpool Ridge North</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Kricketot</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8412,22 +8428,22 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Wayward Cave</t>
+          <t>Cloudpool Ridge North</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Kricketune</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -8437,7 +8453,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8468,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Kricketot</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8462,7 +8478,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8493,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Kricketune</t>
+          <t>Bonsly</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8487,7 +8503,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8518,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Honchkrow</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8512,7 +8528,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8543,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Bonsly</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -8537,7 +8553,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8568,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Honchkrow</t>
+          <t>Wyrdeer</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8562,22 +8578,22 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge North</t>
+          <t>Cloudpool Ridge South</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -8587,7 +8603,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8618,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8627,7 +8643,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8652,7 +8668,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Roserade</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -8677,7 +8693,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Roserade</t>
+          <t>Sudowoodo</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -8693,16 +8709,16 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge South</t>
+          <t>Shrouded Ruins</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Sudowoodo</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -8712,7 +8728,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8743,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -8752,7 +8768,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -8777,7 +8793,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -8802,7 +8818,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Rhyhorn</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -8827,7 +8843,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Rhyhorn</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -8852,7 +8868,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Lickilicky</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -8877,7 +8893,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Lickilicky</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -8893,16 +8909,16 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Shrouded Ruins</t>
+          <t>Space-Time Distortion</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Lickitung</t>
+          <t>Alakazam</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -8912,7 +8928,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8943,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Alakazam</t>
+          <t>Cyndaquil</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8952,7 +8968,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Cyndaquil</t>
+          <t>Eevee</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8977,7 +8993,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Eevee</t>
+          <t>Kadabra</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9002,7 +9018,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Kadabra</t>
+          <t>Oshawott</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9027,7 +9043,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Rhydon</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9052,7 +9068,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Rhydon</t>
+          <t>Rhyperior</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9077,7 +9093,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Rhyperior</t>
+          <t>Rowlet</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9102,7 +9118,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Rowlet</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9127,7 +9143,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Bastiodon</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9152,7 +9168,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Bastiodon</t>
+          <t>Cranidos</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9177,7 +9193,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Cranidos</t>
+          <t>Dartrix</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9202,7 +9218,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Dartrix</t>
+          <t>Decidueye</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -9227,7 +9243,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Decidueye</t>
+          <t>Dewott</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9252,7 +9268,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Dewott</t>
+          <t>Espeon</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -9277,7 +9293,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Espeon</t>
+          <t>Flareon</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -9302,7 +9318,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Flareon</t>
+          <t>Gengar</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -9327,7 +9343,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Gengar</t>
+          <t>Glaceon</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9352,7 +9368,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Glaceon</t>
+          <t>Jolteon</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9377,7 +9393,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Jolteon</t>
+          <t>Leafeon</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9402,7 +9418,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Leafeon</t>
+          <t>Magmortar</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9427,7 +9443,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Magmortar</t>
+          <t>Magnemite</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -9452,7 +9468,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Magnemite</t>
+          <t>Magneton</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -9477,7 +9493,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Magneton</t>
+          <t>Porygon</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9502,7 +9518,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Porygon</t>
+          <t>Porygon-Z</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9527,7 +9543,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Porygon-Z</t>
+          <t>Porygon2</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9552,7 +9568,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Porygon2</t>
+          <t>Quilava</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9577,7 +9593,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Quilava</t>
+          <t>Rampardos</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9602,7 +9618,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Rampardos</t>
+          <t>Samurott</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -9627,7 +9643,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Samurott</t>
+          <t>Scizor</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9652,7 +9668,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Scizor</t>
+          <t>Shieldon</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -9677,7 +9693,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Shieldon</t>
+          <t>Sylveon</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -9702,7 +9718,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Sylveon</t>
+          <t>Typhlosion</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -9727,7 +9743,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Typhlosion</t>
+          <t>Umbreon</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9752,7 +9768,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Umbreon</t>
+          <t>Vaporeon</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -9777,7 +9793,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Vaporeon</t>
+          <t>Weavile</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -9802,7 +9818,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Weavile</t>
+          <t>Kleavor</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9827,7 +9843,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Kleavor</t>
+          <t>Lilligant</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9852,7 +9868,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Lilligant</t>
+          <t>Unown</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -9862,22 +9878,22 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Space-Time Distortion</t>
+          <t>Obsidian Fieldlands Fishing Spot</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Unown</t>
+          <t>Magikarp</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -9887,7 +9903,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -9902,7 +9918,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Magikarp</t>
+          <t>Gyarados</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -9927,7 +9943,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Gyarados</t>
+          <t>Golduck</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -9952,7 +9968,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Golduck</t>
+          <t>Psyduck</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -9977,7 +9993,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Psyduck</t>
+          <t>Buizel</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -9993,16 +10009,16 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Obsidian Fieldlands Fishing Spot</t>
+          <t>Crimson Mirelands Fishing Spot</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Buizel</t>
+          <t>Barboach</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10012,7 +10028,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10043,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Barboach</t>
+          <t>Whiscash</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10052,7 +10068,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Whiscash</t>
+          <t>Togekiss</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10077,7 +10093,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Togekiss</t>
+          <t>Goomy</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10102,7 +10118,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Goomy</t>
+          <t>Sliggoo</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10127,7 +10143,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Sliggoo</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -10137,22 +10153,22 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Crimson Mirelands Fishing Spot</t>
+          <t>Cobalt Coastlands Fishing Spot</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Basculin Red-Striped Form</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -10162,7 +10178,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10193,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Basculin Red-Striped Form</t>
+          <t>Basculegion</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -10202,7 +10218,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Basculegion</t>
+          <t>Qwilfish</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -10227,7 +10243,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Qwilfish</t>
+          <t>Overqwil</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10252,7 +10268,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Overqwil</t>
+          <t>Tentacool</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -10277,7 +10293,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tentacool</t>
+          <t>Tentacruel</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -10302,7 +10318,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Tentacruel</t>
+          <t>Finneon</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -10327,7 +10343,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Finneon</t>
+          <t>Lumineon</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -10343,16 +10359,16 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Cobalt Coastlands Fishing Spot</t>
+          <t>Coronet Highlands Fishing Spot</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Lumineon</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -10362,7 +10378,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10393,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -10402,7 +10418,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Mantyke</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -10427,7 +10443,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mantyke</t>
+          <t>Mantine</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -10452,7 +10468,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mantine</t>
+          <t>Gastrodon</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -10477,7 +10493,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Gastrodon</t>
+          <t>Shellos</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10487,22 +10503,22 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Coronet Highlands Fishing Spot</t>
+          <t>Alabaster Icelands Fishing Spot</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Shellos</t>
+          <t>Spheal</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -10512,7 +10528,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10543,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Spheal</t>
+          <t>Sealeo</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -10552,7 +10568,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Sealeo</t>
+          <t>Walrein</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -10577,7 +10593,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Walrein</t>
+          <t>Piplup</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -10602,7 +10618,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Piplup</t>
+          <t>Prinplup</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -10627,7 +10643,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Prinplup</t>
+          <t>Empoleon</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -10637,22 +10653,22 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Alabaster Icelands Fishing Spot</t>
+          <t>Lake of Trials</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Empoleon</t>
+          <t>Uxie</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -10662,7 +10678,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10693,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Uxie</t>
+          <t>Mesprit</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -10702,7 +10718,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Mesprit</t>
+          <t>Azelf</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10712,22 +10728,22 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Lake of Trials</t>
+          <t>Incarnate Fields</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Azelf</t>
+          <t>Tornadus</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -10737,7 +10753,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -10752,7 +10768,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Tornadus</t>
+          <t>Thundurus</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -10777,7 +10793,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Thundurus</t>
+          <t>Landorus</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -10802,7 +10818,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Landorus</t>
+          <t>Enamorus</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -10818,16 +10834,16 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Incarnate Fields</t>
+          <t>Moonview Arena</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Enamorus</t>
+          <t>Cresselia</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -10837,7 +10853,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -10852,7 +10868,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Cresselia</t>
+          <t>Darkrai</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -10868,16 +10884,16 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Moonview Arena</t>
+          <t>Firespit Island (Inner)</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Darkrai</t>
+          <t>Heatran</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -10887,22 +10903,22 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Firespit Island (Inner)</t>
+          <t>Snowpoint Temple (Basement)</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Heatran</t>
+          <t>Regigigas</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -10918,16 +10934,16 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Snowpoint Temple (Basement)</t>
+          <t>Seaside Hollow</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Regigigas</t>
+          <t>Phione</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10937,7 +10953,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10968,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Phione</t>
+          <t>Manaphy</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -10968,16 +10984,16 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Seaside Hollow</t>
+          <t>Floaro Gardens (Secret)</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Manaphy</t>
+          <t>Shaymin</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -10987,22 +11003,22 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Floaro Gardens (Secret)</t>
+          <t>Shrouded Ruins (Wisp)</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Shaymin</t>
+          <t>Spiritomb</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -11018,16 +11034,16 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Shrouded Ruins (Wisp)</t>
+          <t>Citadel of Etertime</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Spiritomb</t>
+          <t>Arceus</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -11037,7 +11053,82 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>84</v>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Citadel of Etertime</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Dialga</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>84</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Citadel of Etertime</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Palkia</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>84</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Citadel of Etertime</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Giratina</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>30%</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12049,12 +12140,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Sandgem Flats South</t>
+          <t>Defeat Gym - Lilligant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unlock Ramanas Island North</t>
+          <t>Unlock Crimson Mirelands Fishing Spot</t>
         </is>
       </c>
     </row>
@@ -12066,369 +12157,216 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Ramanas Island North</t>
+          <t>Defeat Gym - Arcanine</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unlock Ramanas Island South</t>
+          <t>Unlock Cobalt Coastlands Fishing Spot</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-1</t>
+          <t>Extra Challenge 1-7</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Defeat Gym - Lilligant &amp; Capture 30 Mirelands Pokemon</t>
+          <t>Defeat Gym - Electrode</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unlock Crimson Mirelands Fishing Spot</t>
+          <t>Unlock Coronet Highlands Fishing Spot</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-2</t>
+          <t>Extra Challenge 1-8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Crimson Mirelands Fishing Spot</t>
+          <t>Defeat Gym - Avalugg</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Unlock Droning Meadow</t>
+          <t>Unlock Alabaster Icelands Fishing Spot</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-1</t>
+          <t>Extra Challenge 1-9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Defeat Gym - Arcanine &amp; Capture 30 Coastlands Pokemon</t>
+          <t>Capture 50 Ghost Type Pokemon</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unlock Cobalt Coastlands Fishing Spot</t>
+          <t>Unlock Shrouded Ruins (Wisp)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-2</t>
+          <t>Extra Challenge 1-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Cobalt Coastlands Fishing Spot</t>
+          <t>Enter 10 Space-Time Distortions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unlock Ginkgo Landing</t>
+          <t>Unlock Space-Time Distortion</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-3</t>
+          <t>Extra Challenge 2-1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Ginkgo Landing</t>
+          <t>Defeat Hisui Pokemon League</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unlock Shrouded Ruins</t>
+          <t>Unlock Lake of Trials</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Extra Challenge 4-1</t>
+          <t>Extra Challenge 2-2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Defeat Gym - Electrode &amp; Capture 30 Highlands Pokemon</t>
+          <t>Capture Uxie, Mesprit, Azelf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unlock Coronet Highlands Fishing Spot</t>
+          <t>Unlock Incarnate Fields</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Extra Challenge 4-2</t>
+          <t>Extra Challenge 2-3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Coronet Highlands Fishing Spot</t>
+          <t>Capture Tornadus, Thundurus, Landorus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unlock Cloudpool Ridge North</t>
+          <t>Unlock Moonview Arena</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Extra Challenge 4-3</t>
+          <t>Extra Challenge 2-4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Cloudpool Ridge North</t>
+          <t>Capture Cresselia, Darkrai</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unlock Cloudpool Ridge South</t>
+          <t>Unlock Firespit Island (Inner)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Extra Challenge 4-4</t>
+          <t>Extra Challenge 2-5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Cloudpool Ridge South</t>
+          <t>Capture Heatran</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unlock Wayward Cave</t>
+          <t>Unlock Snowpoint Temple (Basement)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Extra Challenge 5-1</t>
+          <t>Extra Challenge 2-6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Defeat Gym - Avalugg &amp; Capture 30 Icelands Pokemon</t>
+          <t>Capture Regigigas</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unlock Alabaster Icelands Fishing Spot</t>
+          <t>Unlock Seaside Hollow</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Extra Challenge 5-2</t>
+          <t>Extra Challenge 2-7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Alabaster Icelands Fishing Spot</t>
+          <t>Capture Phione, Manaphy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unlock Lake Verity</t>
+          <t>Unlock Floaro Gardens (Secret)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Extra Challenge 5-3</t>
+          <t>Extra Challenge 3-1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Lake Verity</t>
+          <t>Complete All Main &amp; Extra Challenges</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Unlock Lake Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Extra Challenge 6-1</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Defeat Hisui Pokemon League &amp; Enter 10 Distortions</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Unlock Space-Time Distortion</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Extra Challenge 7-1</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Defeat Gym - Avalugg &amp; Capture 50 Ghost Type Pokemon</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Unlock Shrouded Ruins (Wisp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-1</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Defeat Hisui Pokemon League</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Unlock Lake of Trials</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-2</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Capture Uxie, Mesprit, Azelf</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Unlock Incarnate Fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-3</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Capture Tornadus, Thundurus, Landorus</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Unlock Moonview Arena</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-4</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Capture Cresselia, Darkrai</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Unlock Firespit Island (Inner)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-5</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Capture Heatran</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Unlock Snowpoint Temple (Basement)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-6</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Capture Regigigas</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Unlock Seaside Hollow</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Extra Challenge 8-7</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Capture Phione, Manaphy</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Unlock Floaro Gardens (Secret)</t>
+          <t>Unlock Citadel of Etertime</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12471,88 +12409,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dialga</t>
+          <t>Sneasler</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Fighting/Poison</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Space-Time Distortion</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Palkia</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Space-Time Distortion</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Giratina</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Space-Time Distortion</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Arceus</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Space-Time Distortion</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/Hisui_Paths.xlsx
+++ b/Hisui_Paths.xlsx
@@ -1852,28 +1852,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Golden Lowlands South</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Pichu</t>
-        </is>
-      </c>
+          <t>Gym - Clan Leader Adaman</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>23-25</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1882,12 +1874,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pikachu</t>
+          <t>Pichu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1898,7 +1890,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1907,12 +1899,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Pikachu</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1923,7 +1915,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1932,12 +1924,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1948,7 +1940,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1957,12 +1949,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1973,7 +1965,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1982,17 +1974,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>23-25</t>
+          <t>25-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2002,12 +1994,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gapejaw Bog North</t>
+          <t>Golden Lowlands South</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2017,13 +2009,13 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2032,12 +2024,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2048,7 +2040,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2057,12 +2049,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2073,7 +2065,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2082,12 +2074,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2098,7 +2090,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2107,12 +2099,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2123,7 +2115,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -2132,12 +2124,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2148,7 +2140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -2157,17 +2149,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>25-27</t>
+          <t>27-29</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2169,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gapejaw Bog South</t>
+          <t>Gapejaw Bog North</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bibarel</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2192,13 +2184,13 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -2207,12 +2199,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2223,7 +2215,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -2232,12 +2224,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2248,7 +2240,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -2257,12 +2249,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2273,7 +2265,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -2282,12 +2274,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2298,7 +2290,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -2307,12 +2299,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2323,7 +2315,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2332,12 +2324,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2348,7 +2340,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2357,12 +2349,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Yanma</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>27-29</t>
+          <t>29-31</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2377,16 +2369,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gym - Lilligant</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Gapejaw Bog South</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Yanma</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>29-31</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2394,28 +2394,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ursa's Ring</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Bibarel</t>
-        </is>
-      </c>
+          <t>Gym - Lilligant</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>31-33</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2424,12 +2416,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bidoof</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2440,7 +2432,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2449,12 +2441,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Bidoof</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2465,7 +2457,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2474,12 +2466,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2490,7 +2482,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2499,12 +2491,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yanma</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2515,7 +2507,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2524,12 +2516,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Teddiursa</t>
+          <t>Yanma</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2540,7 +2532,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2549,17 +2541,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Petilil</t>
+          <t>Teddiursa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>31-33</t>
+          <t>33-34</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2561,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sludge Mound</t>
+          <t>Ursa's Ring</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Petilil</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2584,7 +2576,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -2594,12 +2586,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Scarlet Bog</t>
+          <t>Sludge Mound</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2609,13 +2601,13 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2624,12 +2616,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2640,7 +2632,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2649,12 +2641,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2665,7 +2657,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2674,12 +2666,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -2690,7 +2682,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2699,12 +2691,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Skuntank</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2715,7 +2707,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2724,17 +2716,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stunky</t>
+          <t>Skuntank</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>34-36</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2736,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Scarlet Bog</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Stunky</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2759,13 +2751,13 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2774,12 +2766,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -2790,7 +2782,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2799,12 +2791,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -2815,7 +2807,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2824,12 +2816,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -2840,7 +2832,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2849,12 +2841,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Onix</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -2865,7 +2857,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2874,12 +2866,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Rhyhorn</t>
+          <t>Onix</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -2890,7 +2882,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2899,17 +2891,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Togetic</t>
+          <t>Rhyhorn</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -2919,12 +2911,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Holm of Trials</t>
+          <t>Bolderoll Slope</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Togetic</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2934,13 +2926,13 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2949,12 +2941,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -2965,7 +2957,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2974,17 +2966,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2986,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Holm of Trials</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Electrode</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3009,13 +3001,13 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -3024,12 +3016,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -3040,7 +3032,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -3049,12 +3041,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -3065,7 +3057,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -3074,12 +3066,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -3090,7 +3082,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -3099,12 +3091,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -3115,7 +3107,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -3124,17 +3116,17 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -3144,12 +3136,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bathers' Lagoon</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Togepi</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3159,13 +3151,13 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -3174,12 +3166,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Togepi</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>44-46</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -3190,7 +3182,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -3199,17 +3191,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>44-46</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3211,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Castaway Shore</t>
+          <t>Bathers' Lagoon</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3234,13 +3226,13 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -3249,12 +3241,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>44-46</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -3265,7 +3257,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -3274,17 +3266,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>44-46</t>
+          <t>46-48</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3294,16 +3286,24 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Gym - Arcanine</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr"/>
+          <t>Castaway Shore</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Skorupi</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>33.4%</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3311,28 +3311,20 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Beautifly</t>
-        </is>
-      </c>
+          <t>Gym - Arcanine</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>48-50</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -3341,12 +3333,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Beautifly</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -3357,7 +3349,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -3366,12 +3358,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dustox</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -3382,7 +3374,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -3391,12 +3383,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Dustox</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -3407,7 +3399,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -3416,12 +3408,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -3432,7 +3424,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -3441,12 +3433,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -3457,7 +3449,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -3466,12 +3458,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -3482,7 +3474,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -3491,12 +3483,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -3507,7 +3499,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -3516,12 +3508,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Growlithe</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -3532,7 +3524,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -3541,12 +3533,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Vulpix</t>
+          <t>Growlithe</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>48-50</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -3561,12 +3553,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tranquility Cove</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Vulpix</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3576,13 +3568,13 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -3591,12 +3583,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>50-51</t>
+          <t>51-53</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -3607,7 +3599,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -3616,17 +3608,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Golem</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>50-51</t>
+          <t>51-53</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3628,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Islespy Shore</t>
+          <t>Tranquility Cove</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3651,57 +3643,49 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Islespy Shore</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Tangrowth</t>
-        </is>
-      </c>
+          <t>Gym - Warden Ingo</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>51-53</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Seagrass Haven</t>
+          <t>Islespy Shore</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>53-55</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3695,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Islespy Shore</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3726,38 +3710,38 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Seagrass Haven</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Torterra</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -3766,12 +3750,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Starly</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -3782,7 +3766,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -3791,12 +3775,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -3807,7 +3791,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -3816,12 +3800,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chatot</t>
+          <t>Starly</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -3832,7 +3816,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -3841,12 +3825,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -3857,7 +3841,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -3866,12 +3850,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dusknoir</t>
+          <t>Chatot</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -3882,7 +3866,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -3891,12 +3875,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>55-57</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -3907,57 +3891,57 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Dusknoir</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Magby</t>
+          <t>Duskull</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3966,12 +3950,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Magmar</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3982,7 +3966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3991,12 +3975,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Magby</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -4007,57 +3991,57 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Magmar</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Ninetales</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -4066,73 +4050,73 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Toxicroak</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -4141,12 +4125,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -4157,7 +4141,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -4166,12 +4150,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4182,7 +4166,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -4191,12 +4175,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4207,7 +4191,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -4216,12 +4200,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chimecho</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -4232,7 +4216,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -4241,12 +4225,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Rhydon</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -4257,7 +4241,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -4266,12 +4250,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Chimecho</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -4282,7 +4266,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -4291,73 +4275,73 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Steelix</t>
+          <t>Rhydon</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bonsly</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Steelix</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -4366,12 +4350,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Bonsly</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -4382,7 +4366,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -4391,12 +4375,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -4407,7 +4391,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -4416,12 +4400,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -4432,7 +4416,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -4441,12 +4425,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -4457,7 +4441,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -4466,12 +4450,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -4482,7 +4466,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -4491,12 +4475,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -4507,20 +4491,28 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Gym - Electrode</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
+          <t>Celestica Ruins</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Misdreavus</t>
+        </is>
+      </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
+          <t>67-68</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4528,12 +4520,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4543,38 +4535,30 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Graveler</t>
-        </is>
-      </c>
+          <t>Gym - Electrode</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>67-68</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -4583,12 +4567,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Gible</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -4599,7 +4583,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -4608,12 +4592,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -4624,7 +4608,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -4633,12 +4617,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -4649,7 +4633,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -4658,73 +4642,73 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Gabite</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Gabite</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -4733,12 +4717,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Luxray</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -4749,7 +4733,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -4758,12 +4742,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -4774,7 +4758,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -4783,12 +4767,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Rotom</t>
+          <t>Luxray</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -4799,7 +4783,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -4808,12 +4792,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -4824,7 +4808,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -4833,12 +4817,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chingling</t>
+          <t>Rotom</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -4849,7 +4833,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -4858,12 +4842,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Rhyperior</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -4874,7 +4858,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -4883,73 +4867,73 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Voltorb</t>
+          <t>Chingling</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>68-70</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Rhyperior</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Voltorb</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -4958,12 +4942,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -4974,7 +4958,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -4983,12 +4967,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -4999,7 +4983,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -5008,12 +4992,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -5024,7 +5008,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -5033,12 +5017,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Mismagius</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -5049,7 +5033,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -5058,12 +5042,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Rotom</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -5074,7 +5058,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -5083,12 +5067,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Torterra</t>
+          <t>Mismagius</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -5099,21 +5083,21 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Rotom</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -5124,21 +5108,21 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Rapidash</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -5149,7 +5133,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -5158,12 +5142,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5174,7 +5158,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -5183,12 +5167,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Scyther</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5199,7 +5183,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -5208,12 +5192,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -5224,7 +5208,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -5233,12 +5217,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Gligar</t>
+          <t>Scyther</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -5249,7 +5233,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -5258,12 +5242,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Gliscor</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5274,7 +5258,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -5283,12 +5267,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Probopass</t>
+          <t>Gligar</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -5299,57 +5283,57 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Goodra</t>
+          <t>Gliscor</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Garchomp</t>
+          <t>Probopass</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -5358,12 +5342,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avalugg</t>
+          <t>Goodra</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -5374,7 +5358,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -5383,12 +5367,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Electivire</t>
+          <t>Garchomp</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -5399,57 +5383,57 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Avalugg</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Electivire</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -5458,12 +5442,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5474,7 +5458,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -5483,12 +5467,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5499,7 +5483,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -5508,12 +5492,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Clefable</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5524,7 +5508,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -5533,12 +5517,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -5549,7 +5533,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -5558,12 +5542,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Clefable</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -5574,7 +5558,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -5583,12 +5567,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -5599,132 +5583,124 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Whiteout Valley</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Cleffa</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Whiteout Valley</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Whiteout Valley</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Whiteout Valley</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Froslass</t>
-        </is>
-      </c>
+          <t>Gym - Clan Leader Irida</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>80-82</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -5733,12 +5709,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Glalie</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -5749,7 +5725,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -5758,12 +5734,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -5774,7 +5750,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -5783,98 +5759,98 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Froslass</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Glalie</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Lopunny</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Swinub</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -5883,12 +5859,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Zoroark</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -5899,7 +5875,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -5908,12 +5884,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Zorua</t>
+          <t>Lopunny</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -5924,99 +5900,99 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Gym - Avalugg</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr"/>
+          <t>Bonechill Wastes South</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Swinub</t>
+        </is>
+      </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr"/>
+          <t>87-89</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Zoroark</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Zorua</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Machop</t>
-        </is>
-      </c>
+          <t>Gym - Avalugg</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>85-87</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -6025,12 +6001,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Crobat</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -6041,7 +6017,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -6050,12 +6026,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Elekid</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -6066,7 +6042,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -6075,12 +6051,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Lucario</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -6091,7 +6067,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -6100,98 +6076,98 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Riolu</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Ambipom</t>
+          <t>Elekid</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Lucario</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Riolu</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -6200,12 +6176,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Ambipom</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6216,7 +6192,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -6225,12 +6201,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Elekid</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6241,7 +6217,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -6250,12 +6226,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Duskull</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6266,7 +6242,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -6275,12 +6251,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6291,7 +6267,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -6300,12 +6276,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bergmite</t>
+          <t>Elekid</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -6316,7 +6292,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -6325,98 +6301,98 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Machamp</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Bergmite</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Machamp</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -6425,12 +6401,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6441,7 +6417,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -6450,12 +6426,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -6466,7 +6442,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -6475,12 +6451,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Abomasnow</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -6491,7 +6467,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -6500,37 +6476,37 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Snover</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>89-91</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -6541,21 +6517,21 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Abomasnow</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -6566,32 +6542,32 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Snover</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -6600,12 +6576,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -6616,7 +6592,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -6625,12 +6601,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Braviary</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -6641,7 +6617,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -6650,12 +6626,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Gallade</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -6666,7 +6642,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -6675,98 +6651,98 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Braviary</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Ambipom</t>
+          <t>Gallade</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -6775,12 +6751,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>99-101</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -6791,7 +6767,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -6800,12 +6776,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Gardevoir</t>
+          <t>Ambipom</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>99-101</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -6816,7 +6792,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -6825,53 +6801,69 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Rapidash</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>99-101</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Gym - Clan Leader Adaman</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
+          <t>Heart's Crag</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Ralts</t>
+        </is>
+      </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr"/>
+          <t>99-101</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Gym - Clan Leader Irida</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
+          <t>Heart's Crag</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Gardevoir</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr"/>
+          <t>99-101</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -6879,16 +6871,24 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Gym - Warden Ingo</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr"/>
+          <t>Heart's Crag</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Ursaring</t>
+        </is>
+      </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr"/>
+          <t>99-101</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>16.5%</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Ursaring</t>
+          <t>Golem</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Golem</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Toxicroak</t>
+          <t>Arcanine</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Arcanine</t>
+          <t>Ursaluna</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ursaluna</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Mamoswine</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Mamoswine</t>
+          <t>Torterra</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Torterra</t>
+          <t>Wyrdeer</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Wyrdeer</t>
+          <t>Sneasler</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Unlock Golden Lowlands South</t>
+          <t>Unlock Gym - Clan Leader Adaman</t>
         </is>
       </c>
     </row>
@@ -11375,12 +11375,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Golden Lowlands South</t>
+          <t>Defeat Gym - Clan Leader Adaman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unlock Gapejaw Bog North</t>
+          <t>Unlock Golden Lowlands South</t>
         </is>
       </c>
     </row>
@@ -11392,12 +11392,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Gapejaw Bog North</t>
+          <t>Defeat 10 Pokemon in Golden Lowlands South</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unlock Gapejaw Bog South</t>
+          <t>Unlock Gapejaw Bog North</t>
         </is>
       </c>
     </row>
@@ -11409,12 +11409,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Gapejaw Bog South</t>
+          <t>Defeat 10 Pokemon in Gapejaw Bog North</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Unlock Gym - Lilligant</t>
+          <t>Unlock Gapejaw Bog South</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Defeat Gym - Lilligant</t>
+          <t>Defeat 10 Pokemon in Gapejaw Bog South</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Unlock Ursa's Ring</t>
+          <t>Unlock Gym - Lilligant</t>
         </is>
       </c>
     </row>
@@ -11443,12 +11443,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Ursa's Ring</t>
+          <t>Defeat Gym - Lilligant</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unlock Sludge Mound</t>
+          <t>Unlock Ursa's Ring</t>
         </is>
       </c>
     </row>
@@ -11460,12 +11460,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Sludge Mound</t>
+          <t>Defeat 10 Pokemon in Ursa's Ring</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Unlock Scarlet Bog</t>
+          <t>Unlock Sludge Mound</t>
         </is>
       </c>
     </row>
@@ -11477,12 +11477,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Scarlet Bog</t>
+          <t>Defeat 10 Pokemon in Sludge Mound</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unlock Bolderoll Slope</t>
+          <t>Unlock Scarlet Bog</t>
         </is>
       </c>
     </row>
@@ -11494,12 +11494,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Bolderoll Slope</t>
+          <t>Defeat 10 Pokemon in Scarlet Bog</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Unlock Holm of Trials</t>
+          <t>Unlock Bolderoll Slope</t>
         </is>
       </c>
     </row>
@@ -11511,12 +11511,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Holm of Trials</t>
+          <t>Defeat 10 Pokemon in Bolderoll Slope</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unlock Crossing Slope</t>
+          <t>Unlock Holm of Trials</t>
         </is>
       </c>
     </row>
@@ -11528,12 +11528,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Crossing Slope</t>
+          <t>Defeat 10 Pokemon in Holm of Trials</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unlock Bathers' Lagoon</t>
+          <t>Unlock Crossing Slope</t>
         </is>
       </c>
     </row>
@@ -11545,12 +11545,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Bathers' Lagoon</t>
+          <t>Defeat 10 Pokemon in Crossing Slope</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unlock Castaway Shore</t>
+          <t>Unlock Bathers' Lagoon</t>
         </is>
       </c>
     </row>
@@ -11562,12 +11562,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Castaway Shore</t>
+          <t>Defeat 10 Pokemon in Bathers' Lagoon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Unlock Gym - Arcanine</t>
+          <t>Unlock Castaway Shore</t>
         </is>
       </c>
     </row>
@@ -11579,12 +11579,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Defeat Gym - Arcanine</t>
+          <t>Defeat 10 Pokemon in Castaway Shore</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Unlock Veilstone Cape</t>
+          <t>Unlock Gym - Arcanine</t>
         </is>
       </c>
     </row>
@@ -11596,12 +11596,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Veilstone Cape</t>
+          <t>Defeat Gym - Arcanine</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unlock Tranquility Cove</t>
+          <t>Unlock Veilstone Cape</t>
         </is>
       </c>
     </row>
@@ -11613,12 +11613,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Tranquility Cove</t>
+          <t>Defeat 10 Pokemon in Veilstone Cape</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unlock Islespy Shore</t>
+          <t>Unlock Tranquility Cove</t>
         </is>
       </c>
     </row>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Islespy Shore</t>
+          <t>Defeat 10 Pokemon in Tranquility Cove</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unlock Seagrass Haven</t>
+          <t>Unlock Gym - Warden Ingo</t>
         </is>
       </c>
     </row>
@@ -11647,12 +11647,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Seagrass Haven</t>
+          <t>Defeat Gym - Warden Ingo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unlock Deadwood Haunt</t>
+          <t>Unlock Islespy Shore</t>
         </is>
       </c>
     </row>
@@ -11664,12 +11664,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Deadwood Haunt</t>
+          <t>Defeat 10 Pokemon in Islespy Shore</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unlock Firespit Island</t>
+          <t>Unlock Seagrass Haven</t>
         </is>
       </c>
     </row>
@@ -11681,12 +11681,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Firespit Island</t>
+          <t>Defeat 10 Pokemon in Seagrass Haven</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unlock Spring Path</t>
+          <t>Unlock Deadwood Haunt</t>
         </is>
       </c>
     </row>
@@ -11698,12 +11698,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Spring Path</t>
+          <t>Defeat 10 Pokemon in Deadwood Haunt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unlock Celestica Trail</t>
+          <t>Unlock Firespit Island</t>
         </is>
       </c>
     </row>
@@ -11715,12 +11715,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Celestica Trail</t>
+          <t>Defeat 10 Pokemon in Firespit Island</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Unlock Celestica Ruins</t>
+          <t>Unlock Spring Path</t>
         </is>
       </c>
     </row>
@@ -11732,12 +11732,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Celestica Ruins</t>
+          <t>Defeat 10 Pokemon in Spring Path</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Unlock Gym - Electrode</t>
+          <t>Unlock Celestica Trail</t>
         </is>
       </c>
     </row>
@@ -11749,12 +11749,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Defeat Gym - Electrode</t>
+          <t>Defeat 10 Pokemon in Celestica Trail</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unlock Clamberclaw Cliffs</t>
+          <t>Unlock Celestica Ruins</t>
         </is>
       </c>
     </row>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Clamberclaw Cliffs</t>
+          <t>Defeat 10 Pokemon in Celestica Ruins</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Unlock Sacred Plaza</t>
+          <t>Unlock Gym - Electrode</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Sacred Plaza</t>
+          <t>Defeat Gym - Electrode</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Unlock Stonetooth Rows</t>
+          <t>Unlock Clamberclaw Cliffs</t>
         </is>
       </c>
     </row>
@@ -11800,12 +11800,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Stonetooth Rows</t>
+          <t>Defeat 10 Pokemon in Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unlock Primeval Grotto</t>
+          <t>Unlock Sacred Plaza</t>
         </is>
       </c>
     </row>
@@ -11817,12 +11817,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Primeval Grotto</t>
+          <t>Defeat 10 Pokemon in Sacred Plaza</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Unlock Coronet Highlands</t>
+          <t>Unlock Stonetooth Rows</t>
         </is>
       </c>
     </row>
@@ -11834,12 +11834,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Coronet Highlands</t>
+          <t>Defeat 10 Pokemon in Stonetooth Rows</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Unlock Fabled Spring</t>
+          <t>Unlock Primeval Grotto</t>
         </is>
       </c>
     </row>
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Fabled Spring</t>
+          <t>Defeat 10 Pokemon in Primeval Grotto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unlock Whiteout Valley</t>
+          <t>Unlock Coronet Highlands</t>
         </is>
       </c>
     </row>
@@ -11868,12 +11868,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Whiteout Valley</t>
+          <t>Defeat 10 Pokemon in Coronet Highlands</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unlock Bonechill Wastes North</t>
+          <t>Unlock Fabled Spring</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Bonechill Wastes North</t>
+          <t>Defeat 10 Pokemon in Fabled Spring</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Unlock Bonechill Wastes South</t>
+          <t>Unlock Whiteout Valley</t>
         </is>
       </c>
     </row>
@@ -11902,12 +11902,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Bonechill Wastes South</t>
+          <t>Defeat 10 Pokemon in Whiteout Valley</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unlock Gym - Avalugg</t>
+          <t>Unlock Gym - Clan Leader Irida</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Defeat Gym - Avalugg</t>
+          <t>Defeat Gym - Clan Leader Irida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unlock Icebound Falls</t>
+          <t>Unlock Bonechill Wastes North</t>
         </is>
       </c>
     </row>
@@ -11936,12 +11936,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Icebound Falls</t>
+          <t>Defeat 10 Pokemon in Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unlock Arena's Approach</t>
+          <t>Unlock Bonechill Wastes South</t>
         </is>
       </c>
     </row>
@@ -11953,12 +11953,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Arena's Approach</t>
+          <t>Defeat 10 Pokemon in Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Unlock Glacier Terrace</t>
+          <t>Unlock Gym - Avalugg</t>
         </is>
       </c>
     </row>
@@ -11970,12 +11970,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Glacier Terrace</t>
+          <t>Defeat Gym - Avalugg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Unlock Snowpoint Temple</t>
+          <t>Unlock Icebound Falls</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Snowpoint Temple</t>
+          <t>Defeat 10 Pokemon in Icebound Falls</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Unlock Heart's Crag</t>
+          <t>Unlock Arena's Approach</t>
         </is>
       </c>
     </row>
@@ -12004,12 +12004,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Heart's Crag</t>
+          <t>Defeat 10 Pokemon in Arena's Approach</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Unlock Gym - Clan Leader Adaman</t>
+          <t>Unlock Glacier Terrace</t>
         </is>
       </c>
     </row>
@@ -12021,12 +12021,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Defeat Gym - Clan Leader Adaman</t>
+          <t>Defeat 10 Pokemon in Glacier Terrace</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Unlock Gym - Clan Leader Irida</t>
+          <t>Unlock Snowpoint Temple</t>
         </is>
       </c>
     </row>
@@ -12038,12 +12038,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Defeat Gym - Clan Leader Irida</t>
+          <t>Defeat 10 Pokemon in Snowpoint Temple</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Unlock Gym - Warden Ingo</t>
+          <t>Unlock Heart's Crag</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Defeat Gym - Warden Ingo</t>
+          <t>Defeat 10 Pokemon in Heart's Crag</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Defeat Gym - Kleavor &amp; Capture 30 Fieldlands Pokemon</t>
+          <t>Capture 30 Fieldlands Pokemon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Defeat Gym - Lilligant</t>
+          <t>Capture 30 Mirelands Pokemon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Defeat Gym - Arcanine</t>
+          <t>Capture 30 Coastlands Pokemon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Defeat Gym - Electrode</t>
+          <t>Capture 30 Highlands Pokemon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Defeat Gym - Avalugg</t>
+          <t>Capture 30 Icelands Pokemon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Enter 10 Space-Time Distortions</t>
+          <t>Capture 200 Pokemon in Total</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -12381,54 +12381,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Pokemon Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Pokemon Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Path to be include</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Obtained?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sneasler</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fighting/Poison</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Celestica Trail</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Hisui_Paths.xlsx
+++ b/Hisui_Paths.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E432"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2601,32 +2601,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Scarlet Bog</t>
+          <t>Sludge Mound</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Electrode</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>36-38</t>
+          <t>34-36</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Skuntank</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Stunky</t>
+          <t>Skuntank</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2751,32 +2751,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bolderoll Slope</t>
+          <t>Scarlet Bog</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Stunky</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>38-40</t>
+          <t>36-38</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Zubat</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Onix</t>
+          <t>Zubat</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rhyhorn</t>
+          <t>Onix</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Togetic</t>
+          <t>Rhyhorn</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2926,32 +2926,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Holm of Trials</t>
+          <t>Bolderoll Slope</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Togetic</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>40-42</t>
+          <t>38-40</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croagunk</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>Croagunk</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Crossing Slope</t>
+          <t>Holm of Trials</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Golem</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>42-44</t>
+          <t>40-42</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tangela</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Tangela</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3151,32 +3151,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bathers' Lagoon</t>
+          <t>Crossing Slope</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Togepi</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>44-46</t>
+          <t>42-44</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Togepi</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Castaway Shore</t>
+          <t>Bathers' Lagoon</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>46-48</t>
+          <t>44-46</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Skorupi</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Gym - Arcanine</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr"/>
+          <t>Castaway Shore</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Skorupi</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>46-48</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>33.4%</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Veilstone Cape</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Beautifly</t>
-        </is>
-      </c>
+          <t>Gym - Arcanine</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>50-51</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Beautifly</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dustox</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Dustox</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Growlithe</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Vulpix</t>
+          <t>Growlithe</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3574,26 +3574,26 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tranquility Cove</t>
+          <t>Veilstone Cape</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Vulpix</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>51-53</t>
+          <t>50-51</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3643,51 +3643,51 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gym - Warden Ingo</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>Tranquility Cove</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tangrowth</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>51-53</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>33.4%</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Islespy Shore</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Murkrow</t>
-        </is>
-      </c>
+          <t>Gym - Warden Ingo</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>55-57</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3716,76 +3716,76 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Seagrass Haven</t>
+          <t>Islespy Shore</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Torterra</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>57-59</t>
+          <t>55-57</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Seagrass Haven</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Torterra</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deadwood Haunt</t>
+          <t>Seagrass Haven</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Ursaring</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>59-61</t>
+          <t>57-59</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Starly</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chatot</t>
+          <t>Starly</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dusknoir</t>
+          <t>Chatot</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3941,51 +3941,51 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Dusknoir</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Firespit Island</t>
+          <t>Deadwood Haunt</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Magby</t>
+          <t>Duskull</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>61-63</t>
+          <t>59-61</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Magmar</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ninetales</t>
+          <t>Magby</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4041,51 +4041,51 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Magmar</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Spring Path</t>
+          <t>Firespit Island</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Ninetales</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>63-65</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Toxicroak</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4110,57 +4110,57 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>65-67</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Celestica Trail</t>
+          <t>Spring Path</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>65-67</t>
+          <t>63-65</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Hippowdon</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Hippowdon</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Chimecho</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Rhydon</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Chimecho</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Steelix</t>
+          <t>Rhydon</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4335,57 +4335,57 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bonsly</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Celestica Ruins</t>
+          <t>Celestica Trail</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Steelix</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>67-68</t>
+          <t>65-67</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Bonsly</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4541,70 +4541,70 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Gym - Electrode</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
+          <t>Celestica Ruins</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Misdreavus</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
+          <t>67-68</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
+          <t>Celestica Ruins</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>70-72</t>
+          <t>67-68</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Clamberclaw Cliffs</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Graveler</t>
-        </is>
-      </c>
+          <t>Gym - Electrode</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>70-72</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Gible</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gabite</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4702,57 +4702,57 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sacred Plaza</t>
+          <t>Clamberclaw Cliffs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Gabite</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>70-72</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Luxray</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Rotom</t>
+          <t>Luxray</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Chingling</t>
+          <t>Rotom</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Rhyperior</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Voltorb</t>
+          <t>Chingling</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4927,57 +4927,57 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bronzong</t>
+          <t>Rhyperior</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Stonetooth Rows</t>
+          <t>Sacred Plaza</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bronzor</t>
+          <t>Voltorb</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>74-76</t>
+          <t>72-74</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Bronzong</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Misdreavus</t>
+          <t>Bronzor</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wormadam Sandy Cloak</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Mismagius</t>
+          <t>Misdreavus</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Rotom</t>
+          <t>Wormadam Sandy Cloak</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Rapidash</t>
+          <t>Mismagius</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5133,21 +5133,21 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Rotom</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -5158,21 +5158,21 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Primeval Grotto</t>
+          <t>Stonetooth Rows</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Rapidash</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>76-78</t>
+          <t>74-76</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Nosepass</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Scyther</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Nosepass</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Gligar</t>
+          <t>Scyther</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Gliscor</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Probopass</t>
+          <t>Gligar</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5333,51 +5333,51 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Goodra</t>
+          <t>Gliscor</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Coronet Highlands</t>
+          <t>Primeval Grotto</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Garchomp</t>
+          <t>Probopass</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>78-80</t>
+          <t>76-78</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avalugg</t>
+          <t>Goodra</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Electivire</t>
+          <t>Garchomp</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5433,51 +5433,51 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Budew</t>
+          <t>Avalugg</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Fabled Spring</t>
+          <t>Coronet Highlands</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Cherrim</t>
+          <t>Electivire</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>80-82</t>
+          <t>78-80</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cherubi</t>
+          <t>Budew</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Cherrim</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Clefable</t>
+          <t>Cherubi</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Clefairy</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cleffa</t>
+          <t>Clefable</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Magnezone</t>
+          <t>Clefairy</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5633,78 +5633,86 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Whiteout Valley</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Cleffa</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Whiteout Valley</t>
+          <t>Fabled Spring</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Snorunt</t>
+          <t>Magnezone</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>82-84</t>
+          <t>80-82</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Gym - Clan Leader Irida</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>Whiteout Valley</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Aipom</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr"/>
+          <t>82-84</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
+          <t>Whiteout Valley</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5714,39 +5722,31 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>85-87</t>
+          <t>82-84</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Bonechill Wastes North</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Wormadam Plant Cloak</t>
-        </is>
-      </c>
+          <t>Gym - Clan Leader Irida</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>85-87</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Froslass</t>
+          <t>Snorunt</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Glalie</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Piloswine</t>
+          <t>Froslass</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Buneary</t>
+          <t>Glalie</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5844,57 +5844,57 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Piloswine</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Bonechill Wastes South</t>
+          <t>Bonechill Wastes North</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Lopunny</t>
+          <t>Buneary</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>87-89</t>
+          <t>85-87</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Swinub</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Zoroark</t>
+          <t>Lopunny</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Zorua</t>
+          <t>Swinub</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5975,70 +5975,70 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Gym - Avalugg</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr"/>
+          <t>Bonechill Wastes South</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Zoroark</t>
+        </is>
+      </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr"/>
+          <t>87-89</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
+          <t>Bonechill Wastes South</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Zorua</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>91-93</t>
+          <t>87-89</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Icebound Falls</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Machoke</t>
-        </is>
-      </c>
+          <t>Gym - Avalugg</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>91-93</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Crobat</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Elekid</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Lucario</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Riolu</t>
+          <t>Elekid</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6161,57 +6161,57 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ambipom</t>
+          <t>Lucario</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Arena's Approach</t>
+          <t>Icebound Falls</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Dusclops</t>
+          <t>Riolu</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>93-95</t>
+          <t>91-93</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Duskull</t>
+          <t>Ambipom</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Electabuzz</t>
+          <t>Dusclops</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Elekid</t>
+          <t>Duskull</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Electabuzz</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Elekid</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bergmite</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Machamp</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6386,57 +6386,57 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Bergmite</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>95-97</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Glacier Terrace</t>
+          <t>Arena's Approach</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Machamp</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>95-97</t>
+          <t>93-95</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Glameow</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Purugly</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Glameow</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Abomasnow</t>
+          <t>Purugly</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Snover</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -6561,27 +6561,27 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Abomasnow</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>97-99</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -6592,26 +6592,26 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Snowpoint Temple</t>
+          <t>Glacier Terrace</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Snover</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>97-99</t>
+          <t>95-97</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Braviary</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Gallade</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Rufflet</t>
+          <t>Braviary</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6736,57 +6736,57 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Gallade</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>99-101</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Heart's Crag</t>
+          <t>Snowpoint Temple</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Ambipom</t>
+          <t>Rufflet</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>99-101</t>
+          <t>97-99</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Ambipom</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Gardevoir</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ursaring</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6886,89 +6886,89 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Hisui Pokemon League</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr"/>
+          <t>Heart's Crag</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Gardevoir</t>
+        </is>
+      </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>101-102</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr"/>
+          <t>99-101</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Worn Bridge</t>
+          <t>Heart's Crag</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Golem</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>99-101</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Worn Bridge</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Golem</t>
-        </is>
-      </c>
+          <t>Hisui Pokemon League</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
+          <t>101-102</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Worn Bridge</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bibarel</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6978,22 +6978,22 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Worn Bridge</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Toxicroak</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7003,22 +7003,22 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Droning Meadow</t>
+          <t>Worn Bridge</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Arcanine</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Grotle</t>
+          <t>Bibarel</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Pachirisu</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Turtwig</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Vespiquen</t>
+          <t>Grotle</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Yanmega</t>
+          <t>Pachirisu</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7159,16 +7159,16 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Droning Meadow</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Beautifly</t>
+          <t>Turtwig</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7184,16 +7184,16 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Droning Meadow</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Burmy Plant Cloak</t>
+          <t>Vespiquen</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7209,16 +7209,16 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Grueling Grove</t>
+          <t>Droning Meadow</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Yanmega</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Dustox</t>
+          <t>Beautifly</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Burmy Plant Cloak</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Heracross</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Dustox</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Toxicroak</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7359,16 +7359,16 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Luxio</t>
+          <t>Heracross</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -7378,22 +7378,22 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Staravia</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7403,22 +7403,22 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Sandgem Flats North</t>
+          <t>Grueling Grove</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Abra</t>
+          <t>Ursaluna</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Luxio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Graveler</t>
+          <t>Staravia</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Luxray</t>
+          <t>Abra</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Arcanine</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -7528,22 +7528,22 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Mime Jr.</t>
+          <t>Graveler</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -7553,22 +7553,22 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Wormadam Plant Cloak</t>
+          <t>Luxray</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -7578,22 +7578,22 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Sandgem Flats South</t>
+          <t>Sandgem Flats North</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Alakazam</t>
+          <t>Tangrowth</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Kadabra</t>
+          <t>Mime Jr.</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mr. Mime</t>
+          <t>Wormadam Plant Cloak</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Snorlax</t>
+          <t>Alakazam</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -7678,22 +7678,22 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Burmy Trash Cloak</t>
+          <t>Kadabra</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Mr. Mime</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ginkgo Landing</t>
+          <t>Sandgem Flats South</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Geodude</t>
+          <t>Snorlax</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Mothim</t>
+          <t>Burmy Trash Cloak</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Starly</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Wormadam Trash Cloak</t>
+          <t>Geodude</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Drapion</t>
+          <t>Mothim</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Ursaluna</t>
+          <t>Starly</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7884,16 +7884,16 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Chimchar</t>
+          <t>Wormadam Trash Cloak</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7903,22 +7903,22 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Drifblim</t>
+          <t>Drapion</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ramanas Island North</t>
+          <t>Ginkgo Landing</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Staravia</t>
+          <t>Mamoswine</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Infernape</t>
+          <t>Chimchar</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Monferno</t>
+          <t>Drifblim</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8009,16 +8009,16 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Ramanas Island South</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Staravia</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8028,22 +8028,22 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Ramanas Island South</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Drifloon</t>
+          <t>Infernape</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8053,22 +8053,22 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Ramanas Island South</t>
+          <t>Ramanas Island North</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Aipom</t>
+          <t>Monferno</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Tangrowth</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8109,16 +8109,16 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Obsidian Falls</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Blissey</t>
+          <t>Drifloon</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8128,22 +8128,22 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Obsidian Falls</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Chansey</t>
+          <t>Aipom</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8153,22 +8153,22 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Obsidian Falls</t>
+          <t>Ramanas Island South</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Happiny</t>
+          <t>Torterra</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Machoke</t>
+          <t>Blissey</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Machop</t>
+          <t>Chansey</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Togepi</t>
+          <t>Happiny</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -8253,22 +8253,22 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Lake Verity</t>
+          <t>Obsidian Falls</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mamoswine</t>
+          <t>Machoke</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -8278,22 +8278,22 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Lake Valor</t>
+          <t>Obsidian Falls</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Torterra</t>
+          <t>Machop</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -8303,22 +8303,22 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Wayward Cave</t>
+          <t>Obsidian Falls</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Golbat</t>
+          <t>Togepi</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -8328,22 +8328,22 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Wayward Cave</t>
+          <t>Lake Verity</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Crobat</t>
+          <t>Wyrdeer</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -8353,22 +8353,22 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Wayward Cave</t>
+          <t>Lake Verity</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Gible</t>
+          <t>Sneasler</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -8378,22 +8378,22 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Wayward Cave</t>
+          <t>Lake Valor</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Wyrdeer</t>
+          <t>Ursaring</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -8403,22 +8403,22 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge North</t>
+          <t>Lake Valor</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Kricketot</t>
+          <t>Rapidash</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -8428,22 +8428,22 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge North</t>
+          <t>Wayward Cave</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Kricketune</t>
+          <t>Golbat</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -8453,22 +8453,22 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge North</t>
+          <t>Wayward Cave</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Roselia</t>
+          <t>Crobat</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -8478,22 +8478,22 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge North</t>
+          <t>Wayward Cave</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Bonsly</t>
+          <t>Gible</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Honchkrow</t>
+          <t>Kricketot</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Murkrow</t>
+          <t>Kricketune</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Sneasler</t>
+          <t>Roselia</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -8578,22 +8578,22 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge South</t>
+          <t>Cloudpool Ridge North</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Bonsly</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -8603,22 +8603,22 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge South</t>
+          <t>Cloudpool Ridge North</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Carnivine</t>
+          <t>Honchkrow</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -8628,22 +8628,22 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Cloudpool Ridge South</t>
+          <t>Cloudpool Ridge North</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Combee</t>
+          <t>Murkrow</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Roserade</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Sudowoodo</t>
+          <t>Carnivine</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -8709,16 +8709,16 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Shrouded Ruins</t>
+          <t>Cloudpool Ridge South</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Burmy Sandy Cloak</t>
+          <t>Combee</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -8728,22 +8728,22 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Shrouded Ruins</t>
+          <t>Cloudpool Ridge South</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Gastly</t>
+          <t>Roserade</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -8753,22 +8753,22 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Shrouded Ruins</t>
+          <t>Cloudpool Ridge South</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Haunter</t>
+          <t>Sudowoodo</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Ralts</t>
+          <t>Burmy Sandy Cloak</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -8818,7 +8818,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Rhyhorn</t>
+          <t>Gastly</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Kirlia</t>
+          <t>Haunter</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Lickilicky</t>
+          <t>Ralts</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Lickitung</t>
+          <t>Rhyhorn</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -8909,16 +8909,16 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Space-Time Distortion</t>
+          <t>Shrouded Ruins</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Alakazam</t>
+          <t>Kirlia</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -8928,22 +8928,22 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Space-Time Distortion</t>
+          <t>Shrouded Ruins</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Cyndaquil</t>
+          <t>Lickilicky</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -8953,22 +8953,22 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Space-Time Distortion</t>
+          <t>Shrouded Ruins</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Eevee</t>
+          <t>Lickitung</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Kadabra</t>
+          <t>Alakazam</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Oshawott</t>
+          <t>Cyndaquil</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Rhydon</t>
+          <t>Eevee</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Rhyperior</t>
+          <t>Kadabra</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Rowlet</t>
+          <t>Oshawott</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Sneasel</t>
+          <t>Rhydon</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Bastiodon</t>
+          <t>Rhyperior</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Cranidos</t>
+          <t>Rowlet</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Dartrix</t>
+          <t>Sneasel</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Decidueye</t>
+          <t>Bastiodon</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Dewott</t>
+          <t>Cranidos</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Espeon</t>
+          <t>Dartrix</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Flareon</t>
+          <t>Decidueye</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Gengar</t>
+          <t>Dewott</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Glaceon</t>
+          <t>Espeon</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Jolteon</t>
+          <t>Flareon</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Leafeon</t>
+          <t>Gengar</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Magmortar</t>
+          <t>Glaceon</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Magnemite</t>
+          <t>Jolteon</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Magneton</t>
+          <t>Leafeon</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Porygon</t>
+          <t>Magmortar</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Porygon-Z</t>
+          <t>Magnemite</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Porygon2</t>
+          <t>Magneton</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Quilava</t>
+          <t>Porygon</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Rampardos</t>
+          <t>Porygon-Z</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Samurott</t>
+          <t>Porygon2</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Scizor</t>
+          <t>Quilava</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Shieldon</t>
+          <t>Rampardos</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Sylveon</t>
+          <t>Samurott</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Typhlosion</t>
+          <t>Scizor</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Umbreon</t>
+          <t>Shieldon</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Vaporeon</t>
+          <t>Sylveon</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Weavile</t>
+          <t>Typhlosion</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Kleavor</t>
+          <t>Umbreon</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Lilligant</t>
+          <t>Vaporeon</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Unown</t>
+          <t>Weavile</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Obsidian Fieldlands Fishing Spot</t>
+          <t>Space-Time Distortion</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Magikarp</t>
+          <t>Kleavor</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -9903,22 +9903,22 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Obsidian Fieldlands Fishing Spot</t>
+          <t>Space-Time Distortion</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Gyarados</t>
+          <t>Lilligant</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -9928,22 +9928,22 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Obsidian Fieldlands Fishing Spot</t>
+          <t>Space-Time Distortion</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Golduck</t>
+          <t>Unown</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Psyduck</t>
+          <t>Magikarp</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Buizel</t>
+          <t>Gyarados</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10009,16 +10009,16 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Crimson Mirelands Fishing Spot</t>
+          <t>Obsidian Fieldlands Fishing Spot</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Barboach</t>
+          <t>Golduck</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10028,22 +10028,22 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Crimson Mirelands Fishing Spot</t>
+          <t>Obsidian Fieldlands Fishing Spot</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Whiscash</t>
+          <t>Psyduck</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10053,22 +10053,22 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Crimson Mirelands Fishing Spot</t>
+          <t>Obsidian Fieldlands Fishing Spot</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Togekiss</t>
+          <t>Buizel</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Goomy</t>
+          <t>Barboach</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Sliggoo</t>
+          <t>Whiscash</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Hippopotas</t>
+          <t>Togekiss</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -10153,22 +10153,22 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Cobalt Coastlands Fishing Spot</t>
+          <t>Crimson Mirelands Fishing Spot</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Basculin Red-Striped Form</t>
+          <t>Goomy</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -10178,22 +10178,22 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Cobalt Coastlands Fishing Spot</t>
+          <t>Crimson Mirelands Fishing Spot</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Basculegion</t>
+          <t>Sliggoo</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -10203,22 +10203,22 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Cobalt Coastlands Fishing Spot</t>
+          <t>Crimson Mirelands Fishing Spot</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Qwilfish</t>
+          <t>Hippopotas</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Overqwil</t>
+          <t>Basculin Red-Striped Form</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Tentacool</t>
+          <t>Basculegion</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Tentacruel</t>
+          <t>Qwilfish</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Finneon</t>
+          <t>Overqwil</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Lumineon</t>
+          <t>Tentacool</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -10359,16 +10359,16 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Coronet Highlands Fishing Spot</t>
+          <t>Cobalt Coastlands Fishing Spot</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Remoraid</t>
+          <t>Tentacruel</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -10378,22 +10378,22 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Coronet Highlands Fishing Spot</t>
+          <t>Cobalt Coastlands Fishing Spot</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Octillery</t>
+          <t>Finneon</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -10403,22 +10403,22 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Coronet Highlands Fishing Spot</t>
+          <t>Cobalt Coastlands Fishing Spot</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mantyke</t>
+          <t>Lumineon</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Mantine</t>
+          <t>Remoraid</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Gastrodon</t>
+          <t>Octillery</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Shellos</t>
+          <t>Mantyke</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -10503,22 +10503,22 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Alabaster Icelands Fishing Spot</t>
+          <t>Coronet Highlands Fishing Spot</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Spheal</t>
+          <t>Mantine</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -10534,16 +10534,16 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Alabaster Icelands Fishing Spot</t>
+          <t>Coronet Highlands Fishing Spot</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Sealeo</t>
+          <t>Gastrodon</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -10559,16 +10559,16 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Alabaster Icelands Fishing Spot</t>
+          <t>Coronet Highlands Fishing Spot</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Walrein</t>
+          <t>Shellos</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10593,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Piplup</t>
+          <t>Spheal</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Prinplup</t>
+          <t>Sealeo</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Empoleon</t>
+          <t>Walrein</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -10653,22 +10653,22 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Lake of Trials</t>
+          <t>Alabaster Icelands Fishing Spot</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Uxie</t>
+          <t>Piplup</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -10678,22 +10678,22 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Lake of Trials</t>
+          <t>Alabaster Icelands Fishing Spot</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Mesprit</t>
+          <t>Prinplup</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -10703,22 +10703,22 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Lake of Trials</t>
+          <t>Alabaster Icelands Fishing Spot</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Azelf</t>
+          <t>Empoleon</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -10728,22 +10728,22 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Incarnate Fields</t>
+          <t>Lake of Trials</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Tornadus</t>
+          <t>Uxie</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -10753,22 +10753,22 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Incarnate Fields</t>
+          <t>Lake of Trials</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Thundurus</t>
+          <t>Mesprit</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -10778,22 +10778,22 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Incarnate Fields</t>
+          <t>Lake of Trials</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Landorus</t>
+          <t>Azelf</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>33.4%</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Enamorus</t>
+          <t>Tornadus</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -10834,16 +10834,16 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Moonview Arena</t>
+          <t>Incarnate Fields</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Cresselia</t>
+          <t>Thundurus</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -10853,22 +10853,22 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Moonview Arena</t>
+          <t>Incarnate Fields</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Darkrai</t>
+          <t>Landorus</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -10878,22 +10878,22 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Firespit Island (Inner)</t>
+          <t>Incarnate Fields</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Heatran</t>
+          <t>Enamorus</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -10903,22 +10903,22 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Snowpoint Temple (Basement)</t>
+          <t>Moonview Arena</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Regigigas</t>
+          <t>Cresselia</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -10928,22 +10928,22 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Seaside Hollow</t>
+          <t>Moonview Arena</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Phione</t>
+          <t>Darkrai</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -10959,16 +10959,16 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Seaside Hollow</t>
+          <t>Firespit Island (Inner)</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Manaphy</t>
+          <t>Heatran</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -10978,22 +10978,22 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Floaro Gardens (Secret)</t>
+          <t>Snowpoint Temple (Basement)</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Shaymin</t>
+          <t>Regigigas</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11009,16 +11009,16 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Shrouded Ruins (Wisp)</t>
+          <t>Seaside Hollow</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Spiritomb</t>
+          <t>Phione</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -11028,22 +11028,22 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Citadel of Etertime</t>
+          <t>Seaside Hollow</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Arceus</t>
+          <t>Manaphy</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -11053,22 +11053,22 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Citadel of Etertime</t>
+          <t>Floaro Gardens (Secret)</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Dialga</t>
+          <t>Shaymin</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -11078,22 +11078,22 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Citadel of Etertime</t>
+          <t>Shrouded Ruins (Wisp)</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Palkia</t>
+          <t>Spiritomb</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -11118,15 +11118,90 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
+          <t>Arceus</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>84</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Citadel of Etertime</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Dialga</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>84</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Citadel of Etertime</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Palkia</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>84</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Citadel of Etertime</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
           <t>Giratina</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -11143,7 +11218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12089,12 +12164,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Obsidian Fieldlands Fishing Spot</t>
+          <t>Capture 30 Mirelands Pokemon</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Unlock Obsidian Falls</t>
+          <t>Unlock Crimson Mirelands Fishing Spot</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12181,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Obsidian Falls</t>
+          <t>Capture 30 Coastlands Pokemon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Unlock Sandgem Flats North</t>
+          <t>Unlock Cobalt Coastlands Fishing Spot</t>
         </is>
       </c>
     </row>
@@ -12123,12 +12198,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Defeat 10 Pokemon in Sandgem Flats North</t>
+          <t>Capture 30 Highlands Pokemon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Unlock Sandgem Flats South</t>
+          <t>Unlock Coronet Highlands Fishing Spot</t>
         </is>
       </c>
     </row>
@@ -12140,231 +12215,299 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capture 30 Mirelands Pokemon</t>
+          <t>Capture 30 Icelands Pokemon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Unlock Crimson Mirelands Fishing Spot</t>
+          <t>Unlock Alabaster Icelands Fishing Spot</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-6</t>
+          <t>Extra Challenge 2-1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capture 30 Coastlands Pokemon</t>
+          <t>Defeat 10 Pokemon in Obsidian Fieldlands Fishing Spot</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unlock Cobalt Coastlands Fishing Spot</t>
+          <t>Unlock Obsidian Falls</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-7</t>
+          <t>Extra Challenge 2-2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capture 30 Highlands Pokemon</t>
+          <t>Defeat 10 Pokemon in Obsidian Falls</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Unlock Coronet Highlands Fishing Spot</t>
+          <t>Unlock Sandgem Flats North</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-8</t>
+          <t>Extra Challenge 2-3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capture 30 Icelands Pokemon</t>
+          <t>Defeat 10 Pokemon in Sandgem Flats North</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Unlock Alabaster Icelands Fishing Spot</t>
+          <t>Unlock Sandgem Flats South</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-9</t>
+          <t>Extra Challenge 2-4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capture 50 Ghost Type Pokemon</t>
+          <t>Defeat 10 Pokemon in Sandgem Flats South</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unlock Shrouded Ruins (Wisp)</t>
+          <t>Unlock Ginkgo Landing</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Extra Challenge 1-10</t>
+          <t>Extra Challenge 3-1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capture 200 Pokemon in Total</t>
+          <t>Capture 50 Ghost Type Pokemon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Unlock Space-Time Distortion</t>
+          <t>Unlock Shrouded Ruins (Wisp)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-1</t>
+          <t>Extra Challenge 3-2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Defeat Hisui Pokemon League</t>
+          <t>Capture 200 Pokemon in Total</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Unlock Lake of Trials</t>
+          <t>Unlock Space-Time Distortion</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-2</t>
+          <t>Extra Challenge 4-1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capture Uxie, Mesprit, Azelf</t>
+          <t>Defeat Hisui Pokemon League</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unlock Incarnate Fields</t>
+          <t>Unlock Lake Verity</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-3</t>
+          <t>Extra Challenge 4-2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capture Tornadus, Thundurus, Landorus</t>
+          <t>Defeat 10 Pokemon in Lake Verity</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unlock Moonview Arena</t>
+          <t>Unlock Lake Valor</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-4</t>
+          <t>Extra Challenge 4-3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capture Cresselia, Darkrai</t>
+          <t>Defeat 10 Pokemon in Lake Valor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unlock Firespit Island (Inner)</t>
+          <t>Unlock Lake of Trials</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-5</t>
+          <t>Extra Challenge 5-1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capture Heatran</t>
+          <t>Defeat Hisui Pokemon League &amp; Capture 50 Flying Type</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Unlock Snowpoint Temple (Basement)</t>
+          <t>Unlock Incarnate Fields</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-6</t>
+          <t>Extra Challenge 6-1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capture Regigigas</t>
+          <t>Defeat Hisui Pokemon League &amp; Capture 50 Rock Type</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Unlock Seaside Hollow</t>
+          <t>Unlock Wayward Cave</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Extra Challenge 2-7</t>
+          <t>Extra Challenge 6-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capture Phione, Manaphy</t>
+          <t>Defeat 10 Pokemon in Wayward Cave</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Unlock Floaro Gardens (Secret)</t>
+          <t>Unlock Snowpoint Temple (Basement)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Extra Challenge 3-1</t>
+          <t>Extra Challenge 7-1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Defeat Hisui Pokemon League &amp; Capture 50 Fire Type</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Unlock Firespit Island (Inner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Extra Challenge 8-1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Defeat Hisui Pokemon League &amp; Capture 50 Dark Type</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Unlock Moonview Arena</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Extra Challenge 9-1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Defeat Hisui Pokemon League &amp; Capture 50 Water Type</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Unlock Seaside Hollow</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Extra Challenge 9-2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Defeat 10 Pokemon in Seaside Hollow</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Unlock Floaro Gardens (Secret)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Extra Challenge 10-1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Complete All Main &amp; Extra Challenges</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Unlock Citadel of Etertime</t>
         </is>
